--- a/05_manual_check/paper_level_summary.xlsx
+++ b/05_manual_check/paper_level_summary.xlsx
@@ -532,7 +532,7 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
@@ -627,7 +627,7 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
@@ -646,7 +646,7 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
@@ -684,7 +684,7 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
@@ -779,7 +779,7 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
@@ -817,7 +817,7 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
